--- a/docs/source/医院内勤规则10.20(1).xlsx
+++ b/docs/source/医院内勤规则10.20(1).xlsx
@@ -376,7 +376,7 @@
     <t>黑龙江省医院（南岗/香坊）</t>
   </si>
   <si>
-    <t>标准价格六折，低温器械（器械包（低温等离子）、器械包（ETO)、单包装包(老肯等温）、单包装包（EO）、额外包（低温等离子）、额外包（ETO)）最高收费180元，超过180元，统一收费180元</t>
+    <t>标准价格六折，低温器械（器械包（低温等离子）、器械包（ETO)、单包装包（老肯低温）、单包装包（EO）、额外包（低温等离子）、额外包（ETO)）最高收费180元，超过180元，统一收费180元</t>
   </si>
   <si>
     <t>呼兰区第一人民医院</t>
